--- a/InputData/trans/AVIC/Annual Vehicle Insurance Cost.xlsx
+++ b/InputData/trans/AVIC/Annual Vehicle Insurance Cost.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeff Rissman\CodeRepositories\eps-us\InputData\trans\AVIC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\India EPS\InputData\trans\AVIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C68CA1-D4E5-4267-A93A-22A2147EC345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6B8FC57-9BAE-4EE0-87FE-1132EFC006F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12870" yWindow="1470" windowWidth="22500" windowHeight="21135" xr2:uid="{D78DFE5E-0A7F-4A12-AD34-4FEABB0CFCE7}"/>
+    <workbookView xWindow="1500" yWindow="1500" windowWidth="19188" windowHeight="11208" xr2:uid="{D78DFE5E-0A7F-4A12-AD34-4FEABB0CFCE7}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="3" r:id="rId2"/>
     <sheet name="AVIC" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,6 +29,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="72">
   <si>
     <t>AVIC Annual Vehicle Insurance Cost</t>
   </si>
@@ -44,18 +46,201 @@
     <t>Source:</t>
   </si>
   <si>
+    <t>Passenger LDVs</t>
+  </si>
+  <si>
     <t>American Automobile Association</t>
   </si>
   <si>
+    <t>Average Annual Cost of New Car Ownership Increases 5% to $9,282</t>
+  </si>
+  <si>
+    <t>https://www.aaa.com/autorepair/articles/average-annual-cost-of-new-vehicle-ownership</t>
+  </si>
+  <si>
+    <t>Freight LDVs</t>
+  </si>
+  <si>
+    <t>Car and Driver magazine</t>
+  </si>
+  <si>
+    <t>Commercial Auto Insurance Cost: Everything You Need to Know</t>
+  </si>
+  <si>
+    <t>https://www.caranddriver.com/car-insurance/a36232977/commercial-auto-insurance-cost/</t>
+  </si>
+  <si>
+    <t>Freight HDVs</t>
+  </si>
+  <si>
+    <t>Progressive Commercial</t>
+  </si>
+  <si>
+    <t>undated</t>
+  </si>
+  <si>
+    <t>What does commercial truck insurance cost?</t>
+  </si>
+  <si>
+    <t>https://www.progressivecommercial.com/commercial-auto-insurance/truck-insurance/commercial-truck-insurance-cost/</t>
+  </si>
+  <si>
+    <t>Passenger HDVs (buses)</t>
+  </si>
+  <si>
+    <t>Bus Insurance HQ</t>
+  </si>
+  <si>
+    <t>https://www.businsurancehq.com/bus-insurance-cost/</t>
+  </si>
+  <si>
+    <t>Passenger Motorbikes</t>
+  </si>
+  <si>
+    <t>Matt Timmons</t>
+  </si>
+  <si>
+    <t>Average Cost of Motorcycle Insurance (2022)</t>
+  </si>
+  <si>
+    <t>https://www.valuepenguin.com/average-cost-of-motorcycle-insurance</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Data on insurnace costs for LDVs, HDVs, and motorbikes is relatively available online, as these vehicles are often</t>
+  </si>
+  <si>
+    <t>used by individuals or small owner-operator businesses (e.g. trucking firms, tourist buses, etc.) that need</t>
+  </si>
+  <si>
+    <t>insurance quotes.</t>
+  </si>
+  <si>
+    <t>Insurance costs for rail, commercial airlines, and freight shipping is harder to come by.  It appears these firms</t>
+  </si>
+  <si>
+    <t>often buy policies covering a broader share of company operations, not just individual vehicles.  For instance,</t>
+  </si>
+  <si>
+    <t>a railroad's insurance might cover up to $X million in damages/liability from covered causes across the railroad's</t>
+  </si>
+  <si>
+    <t>entire system, and would include things like damage caused by spills, collisions, etc.</t>
+  </si>
+  <si>
+    <t>It appears that per-vehicle insurance may not be the correct way to price insurance costs for commercial</t>
+  </si>
+  <si>
+    <t>airlines, rail, or freight shipping, so we leave those values set to zero in this variable.</t>
+  </si>
+  <si>
+    <t>Currency Conversion</t>
+  </si>
+  <si>
+    <t>2019 to 2012 USD</t>
+  </si>
+  <si>
+    <t>2020 to 2012 USD</t>
+  </si>
+  <si>
+    <t>2021 to 2012 USD (est.)</t>
+  </si>
+  <si>
+    <t>Est. 2021 inflation rate (from BLS, through Nov 2021, https://www.bls.gov/cpi/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022 India:US Price level index (ratio of PPP conversion factor (GDP) to market exchange rate), source: https://ourworldindata.org/grapher/gdp-price-levels-relative-to-the-us?tab=table </t>
+  </si>
+  <si>
+    <t>We use PPP conversion rates because it captures the differences in cost of living and adjusts for what $1 can buy in India.</t>
+  </si>
+  <si>
+    <t>Data from AAA:</t>
+  </si>
+  <si>
+    <t>Passenger LDV</t>
+  </si>
+  <si>
+    <t>$/yr (2019 USD)</t>
+  </si>
+  <si>
+    <t>Using data from Car and Driver magazine (2021):</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Simple Avg</t>
+  </si>
+  <si>
+    <t>standard car used for business purposes</t>
+  </si>
+  <si>
+    <t>$/yr (2021 USD)</t>
+  </si>
+  <si>
+    <t>Limousine</t>
+  </si>
+  <si>
+    <t>Cargo or delivery van</t>
+  </si>
+  <si>
+    <t>Taxi</t>
+  </si>
+  <si>
+    <t>Semi-truck</t>
+  </si>
+  <si>
+    <t>For freight LDVs, the value for "cargo or delivery van" is most appropriate.</t>
+  </si>
+  <si>
+    <t>Avg. for specialty truckers</t>
+  </si>
+  <si>
+    <t>$/mth</t>
+  </si>
+  <si>
+    <t>Avg. for transport truckers</t>
+  </si>
+  <si>
+    <t>Overall simple average</t>
+  </si>
+  <si>
+    <t>Annualized</t>
+  </si>
+  <si>
+    <t>$/yr</t>
+  </si>
+  <si>
+    <t>Likely includes primary liability insurance, physical damage insurance, occupational accident coverage, and general liability insurance.</t>
+  </si>
+  <si>
+    <t>For more on these insurance types, see https://www.caranddriver.com/car-insurance/a36320549/truck-insurance-cost/</t>
+  </si>
+  <si>
+    <t>50-state average</t>
+  </si>
+  <si>
+    <t>Timmons (2021):</t>
+  </si>
+  <si>
+    <t>2012 USD/year</t>
+  </si>
+  <si>
+    <t>passenger</t>
+  </si>
+  <si>
+    <t>freight</t>
+  </si>
+  <si>
     <t>LDVs</t>
   </si>
   <si>
-    <t>Average Annual Cost of New Car Ownership Increases 5% to $9,282</t>
-  </si>
-  <si>
-    <t>https://www.aaa.com/autorepair/articles/average-annual-cost-of-new-vehicle-ownership</t>
-  </si>
-  <si>
     <t>HDVs</t>
   </si>
   <si>
@@ -69,183 +254,6 @@
   </si>
   <si>
     <t>motorbikes</t>
-  </si>
-  <si>
-    <t>passenger</t>
-  </si>
-  <si>
-    <t>freight</t>
-  </si>
-  <si>
-    <t>Data from AAA:</t>
-  </si>
-  <si>
-    <t>$/yr (2019 USD)</t>
-  </si>
-  <si>
-    <t>Freight HDVs</t>
-  </si>
-  <si>
-    <t>Progressive Commercial</t>
-  </si>
-  <si>
-    <t>undated</t>
-  </si>
-  <si>
-    <t>What does commercial truck insurance cost?</t>
-  </si>
-  <si>
-    <t>https://www.progressivecommercial.com/commercial-auto-insurance/truck-insurance/commercial-truck-insurance-cost/</t>
-  </si>
-  <si>
-    <t>$/mth</t>
-  </si>
-  <si>
-    <t>Avg. for specialty truckers</t>
-  </si>
-  <si>
-    <t>Avg. for transport truckers</t>
-  </si>
-  <si>
-    <t>Overall simple average</t>
-  </si>
-  <si>
-    <t>Annualized</t>
-  </si>
-  <si>
-    <t>$/yr</t>
-  </si>
-  <si>
-    <t>Passenger LDVs</t>
-  </si>
-  <si>
-    <t>Likely includes primary liability insurance, physical damage insurance, occupational accident coverage, and general liability insurance.</t>
-  </si>
-  <si>
-    <t>For more on these insurance types, see https://www.caranddriver.com/car-insurance/a36320549/truck-insurance-cost/</t>
-  </si>
-  <si>
-    <t>Passenger HDVs (buses)</t>
-  </si>
-  <si>
-    <t>50-state average</t>
-  </si>
-  <si>
-    <t>Bus Insurance HQ</t>
-  </si>
-  <si>
-    <t>https://www.businsurancehq.com/bus-insurance-cost/</t>
-  </si>
-  <si>
-    <t>Freight LDVs</t>
-  </si>
-  <si>
-    <t>Car and Driver magazine</t>
-  </si>
-  <si>
-    <t>https://www.caranddriver.com/car-insurance/a36232977/commercial-auto-insurance-cost/</t>
-  </si>
-  <si>
-    <t>Commercial Auto Insurance Cost: Everything You Need to Know</t>
-  </si>
-  <si>
-    <t>Using data from Car and Driver magazine (2021):</t>
-  </si>
-  <si>
-    <t>standard car used for business purposes</t>
-  </si>
-  <si>
-    <t>Limousine</t>
-  </si>
-  <si>
-    <t>Cargo or delivery van</t>
-  </si>
-  <si>
-    <t>Taxi</t>
-  </si>
-  <si>
-    <t>Semi-truck</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Simple Avg</t>
-  </si>
-  <si>
-    <t>$/yr (2021 USD)</t>
-  </si>
-  <si>
-    <t>For freight LDVs, the value for "cargo or delivery van" is most appropriate.</t>
-  </si>
-  <si>
-    <t>Passenger LDV</t>
-  </si>
-  <si>
-    <t>Passenger Motorbikes</t>
-  </si>
-  <si>
-    <t>Matt Timmons</t>
-  </si>
-  <si>
-    <t>Average Cost of Motorcycle Insurance (2022)</t>
-  </si>
-  <si>
-    <t>https://www.valuepenguin.com/average-cost-of-motorcycle-insurance</t>
-  </si>
-  <si>
-    <t>Timmons (2021):</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Data on insurnace costs for LDVs, HDVs, and motorbikes is relatively available online, as these vehicles are often</t>
-  </si>
-  <si>
-    <t>used by individuals or small owner-operator businesses (e.g. trucking firms, tourist buses, etc.) that need</t>
-  </si>
-  <si>
-    <t>insurance quotes.</t>
-  </si>
-  <si>
-    <t>Insurance costs for rail, commercial airlines, and freight shipping is harder to come by.  It appears these firms</t>
-  </si>
-  <si>
-    <t>often buy policies covering a broader share of company operations, not just individual vehicles.  For instance,</t>
-  </si>
-  <si>
-    <t>a railroad's insurance might cover up to $X million in damages/liability from covered causes across the railroad's</t>
-  </si>
-  <si>
-    <t>entire system, and would include things like damage caused by spills, collisions, etc.</t>
-  </si>
-  <si>
-    <t>It appears that per-vehicle insurance may not be the correct way to price insurance costs for commercial</t>
-  </si>
-  <si>
-    <t>airlines, rail, or freight shipping, so we leave those values set to zero in this variable.</t>
-  </si>
-  <si>
-    <t>Currency Conversion</t>
-  </si>
-  <si>
-    <t>2019 to 2012 USD</t>
-  </si>
-  <si>
-    <t>2020 to 2012 USD</t>
-  </si>
-  <si>
-    <t>2021 to 2012 USD (est.)</t>
-  </si>
-  <si>
-    <t>Est. 2021 inflation rate (from BLS, through Nov 2021, https://www.bls.gov/cpi/)</t>
-  </si>
-  <si>
-    <t>2012 USD/year</t>
   </si>
 </sst>
 </file>
@@ -280,7 +288,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -305,6 +313,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -319,7 +333,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -339,6 +353,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -358,9 +373,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -398,7 +413,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -504,7 +519,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -646,7 +661,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -654,226 +669,241 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC790369-4F84-43C0-97E9-6D0C01E4139F}">
-  <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <v>2021</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B19" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B24" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B26" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B28" s="3">
         <v>2021</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>0.89800000000000002</v>
       </c>
       <c r="B46" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>0.88700000000000001</v>
       </c>
       <c r="B47" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <f>A47/(1+A50)</f>
         <v>0.83052434456928836</v>
       </c>
       <c r="B48" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="9">
         <v>6.8000000000000005E-2</v>
       </c>
       <c r="B50" t="s">
-        <v>68</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -892,48 +922,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C907FFC-9E03-403C-A103-2A580B24C105}">
   <dimension ref="A1:E37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
+    <col min="1" max="1" width="27.44140625" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B4" s="8">
         <v>1194</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>43</v>
       </c>
@@ -944,9 +974,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B11">
         <v>600</v>
@@ -959,12 +989,12 @@
         <v>1500</v>
       </c>
       <c r="E11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B12">
         <v>4000</v>
@@ -977,12 +1007,12 @@
         <v>7000</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B13">
         <v>3300</v>
@@ -995,12 +1025,12 @@
         <v>4750</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B14">
         <v>5000</v>
@@ -1013,12 +1043,12 @@
         <v>7500</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B15">
         <v>8000</v>
@@ -1031,116 +1061,116 @@
         <v>10250</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="B21">
         <v>640</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="B22">
         <v>982</v>
       </c>
       <c r="C22" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="B23">
         <f>AVERAGE(B21:B22)</f>
         <v>811</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="B24" s="8">
         <f>B23*12</f>
         <v>9732</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="B31" s="8">
         <v>9420</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="B37" s="8">
         <v>721</v>
       </c>
       <c r="C37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1154,95 +1184,295 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.140625" customWidth="1"/>
-    <col min="2" max="3" width="12.28515625" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" customWidth="1"/>
+    <col min="2" max="3" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="11">
+        <f>Data!B4*About!A46*About!$A$53</f>
+        <v>310.94147999999996</v>
+      </c>
+      <c r="C2" s="11">
+        <f>Data!D13*About!A48*About!$A$53</f>
+        <v>1144.0472846441946</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="11">
+        <f>Data!B31*About!A48*About!$A$53</f>
+        <v>2268.8264044943817</v>
+      </c>
+      <c r="C3" s="11">
+        <f>Data!B24*About!A48*About!$A$53</f>
+        <v>2343.9722471910113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="13">
+        <v>0</v>
+      </c>
+      <c r="C4" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="11">
-        <f>Data!B4*About!A46</f>
-        <v>1072.212</v>
-      </c>
-      <c r="C2" s="11">
-        <f>Data!D13*About!A48</f>
-        <v>3944.9906367041199</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="11">
-        <f>Data!B31*About!A48</f>
-        <v>7823.5393258426966</v>
-      </c>
-      <c r="C3" s="11">
-        <f>Data!B24*About!A48</f>
-        <v>8082.6629213483147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4">
+      <c r="B5" s="13">
         <v>0</v>
       </c>
-      <c r="C4">
+      <c r="C5" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="13">
         <v>0</v>
       </c>
-      <c r="C5">
+      <c r="C6" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="B7" s="11">
-        <f>Data!B37*About!A48</f>
-        <v>598.80805243445695</v>
-      </c>
-      <c r="C7">
+        <f>Data!B37*About!A48*About!$A$53</f>
+        <v>173.65433520599251</v>
+      </c>
+      <c r="C7" s="13">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71A6F37A-BE2E-4E82-8EB4-94A2AF8D91F1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2967EDB8-467D-4EFC-BDC3-B83C79F932AC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5301B85E-F50F-41BE-AACE-90D8F8AE94CF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{c7ef1c8b-ba63-4702-8e74-5094387a97de}" enabled="0" method="" siteId="{c7ef1c8b-ba63-4702-8e74-5094387a97de}" removed="1"/>
+</clbl:labelList>
 </file>